--- a/config/clone/nature.xlsx
+++ b/config/clone/nature.xlsx
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>权值</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1280,24 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -2290,7 +2273,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>岩</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
